--- a/file/M365_Redemption_-_In-App_Win32_VPATJ07921.xlsx
+++ b/file/M365_Redemption_-_In-App_Win32_VPATJ07921.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E13A793B-943C-4A16-A850-21648A464BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F277A6E-D32A-4F9E-8A79-D61401C1839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="1110" windowWidth="16920" windowHeight="13930" xr2:uid="{827A69AF-F18A-4149-97A0-FF4CAF4D00C6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6900C5DB-2F62-4F06-965C-4C114FCBA431}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="233">
   <si>
     <r>
       <t>ICT</t>
@@ -89,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2</t>
+      <t>6</t>
     </r>
     <r>
       <rPr>
@@ -108,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>20</t>
+      <t>29</t>
     </r>
     <r>
       <rPr>
@@ -590,9 +593,6 @@
       </rPr>
       <t>対応している</t>
     </r>
-    <rPh sb="0" eb="2">
-      <t>タイオウ</t>
-    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -604,98 +604,72 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた器用さ又は力での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた手の届く範囲での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
       <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2631,7 +2605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ABF0347-61E1-4533-AA5C-E0E852371647}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354C5D19-BACA-4850-BB47-D59BCB786C52}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2933,7 +2907,7 @@
       <c r="H21" s="46"/>
       <c r="I21" s="47"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="34" t="s">
         <v>25</v>
       </c>
@@ -3032,30 +3006,30 @@
       <c r="D28" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
+      <c r="E28" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="43"/>
       <c r="D29" s="49"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="47"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="35"/>
       <c r="C30" s="36"/>
@@ -3072,7 +3046,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="43"/>
@@ -3085,7 +3059,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="35"/>
       <c r="C32" s="36"/>
@@ -3098,7 +3072,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="43"/>
@@ -3111,15 +3085,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="35"/>
       <c r="C34" s="36"/>
       <c r="D34" s="44" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
@@ -3128,7 +3102,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" s="42"/>
       <c r="C35" s="43"/>
@@ -3169,15 +3143,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38" s="35"/>
       <c r="C38" s="36"/>
       <c r="D38" s="44" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F38" s="44"/>
       <c r="G38" s="44"/>
@@ -3186,7 +3160,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B39" s="42"/>
       <c r="C39" s="43"/>
@@ -3210,7 +3184,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3240,15 +3214,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B43" s="35"/>
       <c r="C43" s="36"/>
       <c r="D43" s="44" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E43" s="44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F43" s="44"/>
       <c r="G43" s="44"/>
@@ -3257,7 +3231,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="43"/>
@@ -3281,10 +3255,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="56" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B46" s="44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="44"/>
@@ -3307,7 +3281,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="56" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B48" s="44"/>
       <c r="C48" s="44"/>
@@ -3447,8 +3421,8 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" display="https://www.microsoft.com/ja-jp/microsoft-365" xr:uid="{ACC2FD59-B3D5-463A-B52D-2CFEBEE29748}"/>
-    <hyperlink ref="B14:E14" r:id="rId2" display="https://learn.microsoft.com/ja-jp/mem/intune-service/apps/apps-add-office365" xr:uid="{5CB3A6BF-9824-4D12-BA88-4D1A18E9EB3C}"/>
+    <hyperlink ref="B14" r:id="rId1" display="https://www.microsoft.com/ja-jp/microsoft-365" xr:uid="{47C33818-FBBB-4BF1-B107-1F6A8CB629EB}"/>
+    <hyperlink ref="B14:E14" r:id="rId2" display="https://learn.microsoft.com/ja-jp/mem/intune-service/apps/apps-add-office365" xr:uid="{446AE047-8A22-4EDE-8A1B-204B4BB51907}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId3"/>
@@ -3456,7 +3430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDF4B58A-C106-4407-93A9-9CA89AA85518}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392184DD-2BBD-4F43-94A3-3FC011EE4345}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3469,43 +3443,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="D1" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="E1" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="F1" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="G1" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="H1" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="I1" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="J1" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="62" t="s">
+      <c r="K1" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="L1" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="M1" s="62" t="s">
         <v>63</v>
-      </c>
-      <c r="L1" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="62" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3513,36 +3487,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" s="67"/>
       <c r="E2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2" s="69"/>
       <c r="H2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M2" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3550,10 +3524,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3" s="67"/>
       <c r="E3" s="68"/>
@@ -3571,14 +3545,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" s="67"/>
       <c r="E4" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F4" s="67"/>
       <c r="G4" s="70"/>
@@ -3594,15 +3568,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
       <c r="F5" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G5" s="70"/>
       <c r="H5" s="67"/>
@@ -3617,15 +3591,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D6" s="67"/>
       <c r="E6" s="67"/>
       <c r="F6" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G6" s="70"/>
       <c r="H6" s="67"/>
@@ -3640,17 +3614,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="66" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" s="67"/>
       <c r="E7" s="67"/>
       <c r="F7" s="67"/>
       <c r="G7" s="70"/>
       <c r="H7" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I7" s="67"/>
       <c r="J7" s="67"/>
@@ -3663,10 +3637,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" s="67"/>
       <c r="E8" s="67"/>
@@ -3674,7 +3648,7 @@
       <c r="G8" s="70"/>
       <c r="H8" s="67"/>
       <c r="I8" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J8" s="67"/>
       <c r="K8" s="67"/>
@@ -3686,10 +3660,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D9" s="67"/>
       <c r="E9" s="67"/>
@@ -3698,7 +3672,7 @@
       <c r="H9" s="67"/>
       <c r="I9" s="67"/>
       <c r="J9" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K9" s="67"/>
       <c r="L9" s="67"/>
@@ -3709,10 +3683,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" s="67"/>
       <c r="E10" s="67"/>
@@ -3722,10 +3696,10 @@
       <c r="I10" s="67"/>
       <c r="J10" s="67"/>
       <c r="K10" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L10" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M10" s="67"/>
     </row>
@@ -3734,10 +3708,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C11" s="66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D11" s="67"/>
       <c r="E11" s="67"/>
@@ -3747,10 +3721,10 @@
       <c r="I11" s="67"/>
       <c r="J11" s="67"/>
       <c r="K11" s="67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L11" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M11" s="67"/>
     </row>
@@ -3759,10 +3733,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" s="67"/>
       <c r="E12" s="67"/>
@@ -3780,17 +3754,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" s="67"/>
       <c r="E13" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F13" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="68"/>
@@ -3805,10 +3779,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" s="73"/>
       <c r="E14" s="68"/>
@@ -3826,10 +3800,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D15" s="67"/>
       <c r="E15" s="68"/>
@@ -3844,17 +3818,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="66" t="s">
         <v>94</v>
-      </c>
-      <c r="B16" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="66" t="s">
-        <v>96</v>
       </c>
       <c r="D16" s="67"/>
       <c r="E16" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F16" s="67"/>
       <c r="G16" s="70"/>
@@ -3867,17 +3841,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="66" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>99</v>
       </c>
       <c r="D17" s="67"/>
       <c r="E17" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="67"/>
       <c r="G17" s="70"/>
@@ -3890,20 +3864,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="66" t="s">
         <v>100</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="66" t="s">
-        <v>102</v>
       </c>
       <c r="D18" s="67"/>
       <c r="E18" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F18" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G18" s="70"/>
       <c r="H18" s="67"/>
@@ -3915,20 +3889,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="66" t="s">
         <v>103</v>
-      </c>
-      <c r="B19" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="66" t="s">
-        <v>105</v>
       </c>
       <c r="D19" s="67"/>
       <c r="E19" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G19" s="70"/>
       <c r="H19" s="67"/>
@@ -3940,17 +3914,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="66" t="s">
         <v>106</v>
-      </c>
-      <c r="B20" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="66" t="s">
-        <v>108</v>
       </c>
       <c r="D20" s="67"/>
       <c r="E20" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F20" s="67"/>
       <c r="G20" s="70"/>
@@ -3966,10 +3940,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C21" s="66" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" s="67"/>
       <c r="E21" s="67"/>
@@ -3977,7 +3951,7 @@
       <c r="G21" s="70"/>
       <c r="H21" s="67"/>
       <c r="I21" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J21" s="67"/>
       <c r="K21" s="67"/>
@@ -3986,23 +3960,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="66" t="s">
         <v>111</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="66" t="s">
-        <v>113</v>
       </c>
       <c r="D22" s="67"/>
       <c r="E22" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F22" s="67"/>
       <c r="G22" s="70"/>
       <c r="H22" s="67"/>
       <c r="I22" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J22" s="67"/>
       <c r="K22" s="67"/>
@@ -4011,23 +3985,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="66" t="s">
         <v>114</v>
-      </c>
-      <c r="B23" s="66" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="66" t="s">
-        <v>116</v>
       </c>
       <c r="D23" s="67"/>
       <c r="E23" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F23" s="67"/>
       <c r="G23" s="70"/>
       <c r="H23" s="67"/>
       <c r="I23" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J23" s="67"/>
       <c r="K23" s="67"/>
@@ -4039,15 +4013,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D24" s="67"/>
       <c r="E24" s="67"/>
       <c r="F24" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G24" s="70"/>
       <c r="H24" s="67"/>
@@ -4062,15 +4036,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D25" s="67"/>
       <c r="E25" s="67"/>
       <c r="F25" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G25" s="70"/>
       <c r="H25" s="67"/>
@@ -4085,27 +4059,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D26" s="67"/>
       <c r="E26" s="68"/>
       <c r="F26" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G26" s="69"/>
       <c r="H26" s="68"/>
       <c r="I26" s="68"/>
       <c r="J26" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K26" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L26" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M26" s="68"/>
     </row>
@@ -4114,10 +4088,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D27" s="67"/>
       <c r="E27" s="68"/>
@@ -4135,29 +4109,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D28" s="67"/>
       <c r="E28" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F28" s="68"/>
       <c r="G28" s="69"/>
       <c r="H28" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I28" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J28" s="68"/>
       <c r="K28" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L28" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M28" s="68"/>
     </row>
@@ -4166,10 +4140,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D29" s="67"/>
       <c r="E29" s="68"/>
@@ -4187,17 +4161,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C30" s="66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D30" s="67"/>
       <c r="E30" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F30" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G30" s="69"/>
       <c r="H30" s="68"/>
@@ -4212,10 +4186,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D31" s="67"/>
       <c r="E31" s="68"/>
@@ -4233,30 +4207,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D32" s="67"/>
       <c r="E32" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F32" s="68"/>
       <c r="G32" s="69"/>
       <c r="H32" s="68"/>
       <c r="I32" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J32" s="68"/>
       <c r="K32" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L32" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M32" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4264,10 +4238,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C33" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D33" s="67"/>
       <c r="E33" s="68"/>
@@ -4285,31 +4259,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D34" s="67"/>
       <c r="E34" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F34" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G34" s="69"/>
       <c r="H34" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I34" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J34" s="68"/>
       <c r="K34" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L34" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M34" s="68"/>
     </row>
@@ -4318,10 +4292,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D35" s="67"/>
       <c r="E35" s="68"/>
@@ -4339,15 +4313,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="66" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C36" s="66" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D36" s="67"/>
       <c r="E36" s="67"/>
       <c r="F36" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G36" s="70"/>
       <c r="H36" s="67"/>
@@ -4362,14 +4336,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D37" s="67"/>
       <c r="E37" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F37" s="67"/>
       <c r="G37" s="70"/>
@@ -4385,10 +4359,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="66" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D38" s="67"/>
       <c r="E38" s="67"/>
@@ -4398,10 +4372,10 @@
       <c r="I38" s="67"/>
       <c r="J38" s="67"/>
       <c r="K38" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L38" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M38" s="67"/>
     </row>
@@ -4410,27 +4384,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="66" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D39" s="67"/>
       <c r="E39" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F39" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G39" s="70"/>
       <c r="H39" s="67"/>
       <c r="I39" s="67"/>
       <c r="J39" s="67"/>
       <c r="K39" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L39" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M39" s="67"/>
     </row>
@@ -4439,10 +4413,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="66" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C40" s="66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D40" s="67"/>
       <c r="E40" s="67"/>
@@ -4452,10 +4426,10 @@
       <c r="I40" s="67"/>
       <c r="J40" s="67"/>
       <c r="K40" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L40" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M40" s="67"/>
     </row>
@@ -4464,14 +4438,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D41" s="67"/>
       <c r="E41" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F41" s="67"/>
       <c r="G41" s="70"/>
@@ -4487,10 +4461,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="66" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C42" s="66" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D42" s="67"/>
       <c r="E42" s="67"/>
@@ -4500,10 +4474,10 @@
       <c r="I42" s="67"/>
       <c r="J42" s="67"/>
       <c r="K42" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L42" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M42" s="67"/>
     </row>
@@ -4512,10 +4486,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D43" s="68"/>
       <c r="E43" s="68"/>
@@ -4525,10 +4499,10 @@
       <c r="I43" s="68"/>
       <c r="J43" s="68"/>
       <c r="K43" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L43" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M43" s="68"/>
     </row>
@@ -4537,10 +4511,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C44" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D44" s="68"/>
       <c r="E44" s="68"/>
@@ -4558,10 +4532,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="66" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C45" s="66" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D45" s="68"/>
       <c r="E45" s="68"/>
@@ -4579,10 +4553,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="66" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C46" s="66" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
@@ -4600,14 +4574,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="66" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C47" s="66" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D47" s="67"/>
       <c r="E47" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F47" s="68"/>
       <c r="G47" s="69"/>
@@ -4623,10 +4597,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C48" s="66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D48" s="67"/>
       <c r="E48" s="68"/>
@@ -4644,15 +4618,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="66" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D49" s="67"/>
       <c r="E49" s="68"/>
       <c r="F49" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G49" s="69"/>
       <c r="H49" s="68"/>
@@ -4667,10 +4641,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C50" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D50" s="67"/>
       <c r="E50" s="68"/>
@@ -4688,20 +4662,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="66" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C51" s="66" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D51" s="67"/>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
       <c r="G51" s="69"/>
       <c r="H51" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I51" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J51" s="68"/>
       <c r="K51" s="68"/>
@@ -4713,10 +4687,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C52" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D52" s="67"/>
       <c r="E52" s="68"/>
@@ -4734,29 +4708,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="66" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C53" s="66" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D53" s="67"/>
       <c r="E53" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F53" s="68"/>
       <c r="G53" s="69"/>
       <c r="H53" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I53" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J53" s="68"/>
       <c r="K53" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L53" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M53" s="68"/>
     </row>
@@ -4765,10 +4739,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C54" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D54" s="67"/>
       <c r="E54" s="68"/>
@@ -4786,10 +4760,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="66" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C55" s="66" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D55" s="67"/>
       <c r="E55" s="67"/>
@@ -4797,7 +4771,7 @@
       <c r="G55" s="70"/>
       <c r="H55" s="67"/>
       <c r="I55" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J55" s="67"/>
       <c r="K55" s="67"/>
@@ -4809,10 +4783,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C56" s="66" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D56" s="67"/>
       <c r="E56" s="67"/>
@@ -4820,7 +4794,7 @@
       <c r="G56" s="70"/>
       <c r="H56" s="67"/>
       <c r="I56" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J56" s="67"/>
       <c r="K56" s="67"/>
@@ -4832,10 +4806,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="66" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C57" s="66" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D57" s="67"/>
       <c r="E57" s="67"/>
@@ -4843,7 +4817,7 @@
       <c r="G57" s="70"/>
       <c r="H57" s="67"/>
       <c r="I57" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J57" s="67"/>
       <c r="K57" s="67"/>
@@ -4855,10 +4829,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="66" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C58" s="66" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D58" s="67"/>
       <c r="E58" s="67"/>
@@ -4876,24 +4850,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="66" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C59" s="66" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D59" s="67"/>
       <c r="E59" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F59" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G59" s="70"/>
       <c r="H59" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I59" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J59" s="67"/>
       <c r="K59" s="67"/>
@@ -4905,17 +4879,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C60" s="66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D60" s="67"/>
       <c r="E60" s="67"/>
       <c r="F60" s="67"/>
       <c r="G60" s="70"/>
       <c r="H60" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I60" s="67"/>
       <c r="J60" s="67"/>
@@ -4928,20 +4902,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="66" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C61" s="66" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D61" s="67"/>
       <c r="E61" s="68"/>
       <c r="F61" s="68"/>
       <c r="G61" s="69"/>
       <c r="H61" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I61" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J61" s="68"/>
       <c r="K61" s="68"/>
@@ -4953,10 +4927,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="66" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C62" s="66" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D62" s="67"/>
       <c r="E62" s="68"/>
@@ -4974,14 +4948,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="66" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C63" s="66" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D63" s="67"/>
       <c r="E63" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F63" s="68"/>
       <c r="G63" s="69"/>
@@ -4997,10 +4971,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="66" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C64" s="66" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D64" s="67"/>
       <c r="E64" s="68"/>
@@ -5018,22 +4992,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="66" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C65" s="66" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D65" s="67"/>
       <c r="E65" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F65" s="68"/>
       <c r="G65" s="69"/>
       <c r="H65" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I65" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J65" s="68"/>
       <c r="K65" s="68"/>
@@ -5045,10 +5019,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="66" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C66" s="66" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D66" s="67"/>
       <c r="E66" s="68"/>
@@ -5066,31 +5040,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C67" s="66" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D67" s="67"/>
       <c r="E67" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F67" s="68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G67" s="69"/>
       <c r="H67" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I67" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J67" s="68"/>
       <c r="K67" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L67" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M67" s="68"/>
     </row>
@@ -5099,10 +5073,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C68" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D68" s="67"/>
       <c r="E68" s="68"/>
@@ -5120,29 +5094,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="66" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C69" s="66" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D69" s="67"/>
       <c r="E69" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F69" s="67"/>
       <c r="G69" s="70"/>
       <c r="H69" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I69" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J69" s="67"/>
       <c r="K69" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L69" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M69" s="67"/>
     </row>
@@ -5151,14 +5125,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="C70" s="66" t="s">
         <v>187</v>
-      </c>
-      <c r="C70" s="66" t="s">
-        <v>189</v>
       </c>
       <c r="D70" s="67"/>
       <c r="E70" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F70" s="67"/>
       <c r="G70" s="70"/>
@@ -5166,10 +5140,10 @@
       <c r="I70" s="67"/>
       <c r="J70" s="67"/>
       <c r="K70" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L70" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M70" s="67"/>
     </row>
@@ -5178,43 +5152,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="66" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C71" s="66" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D71" s="67"/>
       <c r="E71" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F71" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G71" s="70"/>
       <c r="H71" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I71" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J71" s="67"/>
       <c r="K71" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L71" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M71" s="67"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B72" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="C72" s="66" t="s">
         <v>192</v>
-      </c>
-      <c r="B72" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="C72" s="66" t="s">
-        <v>194</v>
       </c>
       <c r="D72" s="67"/>
       <c r="E72" s="67"/>
@@ -5224,22 +5198,22 @@
       <c r="I72" s="67"/>
       <c r="J72" s="67"/>
       <c r="K72" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L72" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M72" s="67"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="C73" s="66" t="s">
         <v>195</v>
-      </c>
-      <c r="B73" s="66" t="s">
-        <v>196</v>
-      </c>
-      <c r="C73" s="66" t="s">
-        <v>197</v>
       </c>
       <c r="D73" s="67"/>
       <c r="E73" s="67"/>
@@ -5249,22 +5223,22 @@
       <c r="I73" s="67"/>
       <c r="J73" s="67"/>
       <c r="K73" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L73" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M73" s="67"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C74" s="66" t="s">
         <v>198</v>
-      </c>
-      <c r="B74" s="66" t="s">
-        <v>199</v>
-      </c>
-      <c r="C74" s="66" t="s">
-        <v>200</v>
       </c>
       <c r="D74" s="67"/>
       <c r="E74" s="67"/>
@@ -5274,32 +5248,32 @@
       <c r="I74" s="67"/>
       <c r="J74" s="67"/>
       <c r="K74" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L74" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M74" s="67"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="C75" s="66" t="s">
         <v>201</v>
-      </c>
-      <c r="B75" s="66" t="s">
-        <v>202</v>
-      </c>
-      <c r="C75" s="66" t="s">
-        <v>203</v>
       </c>
       <c r="D75" s="67"/>
       <c r="E75" s="67"/>
       <c r="F75" s="67"/>
       <c r="G75" s="70"/>
       <c r="H75" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I75" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J75" s="67"/>
       <c r="K75" s="67"/>
@@ -5308,23 +5282,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="B76" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C76" s="66" t="s">
         <v>204</v>
-      </c>
-      <c r="B76" s="66" t="s">
-        <v>205</v>
-      </c>
-      <c r="C76" s="66" t="s">
-        <v>206</v>
       </c>
       <c r="D76" s="67"/>
       <c r="E76" s="67"/>
       <c r="F76" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G76" s="70"/>
       <c r="H76" s="67"/>
       <c r="I76" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J76" s="67"/>
       <c r="K76" s="67"/>
@@ -5333,26 +5307,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="B77" s="66" t="s">
+        <v>206</v>
+      </c>
+      <c r="C77" s="66" t="s">
         <v>207</v>
-      </c>
-      <c r="B77" s="66" t="s">
-        <v>208</v>
-      </c>
-      <c r="C77" s="66" t="s">
-        <v>209</v>
       </c>
       <c r="D77" s="67"/>
       <c r="E77" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F77" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G77" s="70"/>
       <c r="H77" s="67"/>
       <c r="I77" s="67"/>
       <c r="J77" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K77" s="67"/>
       <c r="L77" s="67"/>
@@ -5360,23 +5334,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="B78" s="66" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="66" t="s">
         <v>210</v>
-      </c>
-      <c r="B78" s="66" t="s">
-        <v>211</v>
-      </c>
-      <c r="C78" s="66" t="s">
-        <v>212</v>
       </c>
       <c r="D78" s="67"/>
       <c r="E78" s="67"/>
       <c r="F78" s="67"/>
       <c r="G78" s="70"/>
       <c r="H78" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I78" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J78" s="67"/>
       <c r="K78" s="67"/>
@@ -5388,31 +5362,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="66" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C79" s="66" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D79" s="67"/>
       <c r="E79" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F79" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G79" s="69"/>
       <c r="H79" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I79" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J79" s="68"/>
       <c r="K79" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L79" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M79" s="68"/>
     </row>
@@ -5421,10 +5395,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C80" s="66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D80" s="67"/>
       <c r="E80" s="68"/>
@@ -5442,15 +5416,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="66" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C81" s="66" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D81" s="67"/>
       <c r="E81" s="67"/>
       <c r="F81" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G81" s="70"/>
       <c r="H81" s="67"/>
@@ -5465,14 +5439,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="66" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C82" s="66" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D82" s="67"/>
       <c r="E82" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F82" s="67"/>
       <c r="G82" s="70"/>
@@ -5480,10 +5454,10 @@
       <c r="I82" s="67"/>
       <c r="J82" s="67"/>
       <c r="K82" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L82" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M82" s="67"/>
     </row>
@@ -5492,22 +5466,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="66" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D83" s="67"/>
       <c r="E83" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F83" s="67"/>
       <c r="G83" s="70"/>
       <c r="H83" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I83" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J83" s="67"/>
       <c r="K83" s="67"/>
@@ -5519,24 +5493,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="66" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C84" s="66" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D84" s="67"/>
       <c r="E84" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F84" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G84" s="69"/>
       <c r="H84" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I84" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J84" s="68"/>
       <c r="K84" s="68"/>
@@ -5548,10 +5522,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C85" s="66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D85" s="67"/>
       <c r="E85" s="68"/>
@@ -5569,24 +5543,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="66" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C86" s="66" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D86" s="67"/>
       <c r="E86" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F86" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G86" s="70"/>
       <c r="H86" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I86" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J86" s="67"/>
       <c r="K86" s="67"/>
@@ -5595,25 +5569,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="B87" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C87" s="66" t="s">
         <v>225</v>
-      </c>
-      <c r="B87" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="C87" s="66" t="s">
-        <v>227</v>
       </c>
       <c r="D87" s="67"/>
       <c r="E87" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F87" s="67"/>
       <c r="G87" s="70"/>
       <c r="H87" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I87" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J87" s="67"/>
       <c r="K87" s="67"/>
@@ -5622,20 +5596,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="B88" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="C88" s="66" t="s">
         <v>228</v>
-      </c>
-      <c r="B88" s="66" t="s">
-        <v>229</v>
-      </c>
-      <c r="C88" s="66" t="s">
-        <v>230</v>
       </c>
       <c r="D88" s="67"/>
       <c r="E88" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F88" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G88" s="70"/>
       <c r="H88" s="67"/>
@@ -5650,24 +5624,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="66" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C89" s="66" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D89" s="67"/>
       <c r="E89" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F89" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G89" s="70"/>
       <c r="H89" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I89" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J89" s="67"/>
       <c r="K89" s="67"/>
@@ -5679,24 +5653,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="66" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C90" s="66" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D90" s="67"/>
       <c r="E90" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F90" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G90" s="70"/>
       <c r="H90" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I90" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J90" s="67"/>
       <c r="K90" s="67"/>
